--- a/artfynd/A 34604-2026 artfynd.xlsx
+++ b/artfynd/A 34604-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ11"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1812,6 +1812,118 @@
       <c r="AZ11" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137093771</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137123335</v>
+      </c>
+      <c r="B12" t="n">
+        <v>101572</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Örsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>674763</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6634096</v>
+      </c>
+      <c r="S12" t="n">
+        <v>8</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Husby-Långhundra</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Ylva Petersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Ylva Petersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137123335</t>
         </is>
       </c>
     </row>
@@ -1827,6 +1939,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34604-2026 artfynd.xlsx
+++ b/artfynd/A 34604-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093774</v>
       </c>
       <c r="B2" t="n">
-        <v>96574</v>
+        <v>96580</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137093765</v>
       </c>
       <c r="B3" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137093773</v>
       </c>
       <c r="B4" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>137093772</v>
       </c>
       <c r="B9" t="n">
-        <v>98218</v>
+        <v>98224</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>137093767</v>
       </c>
       <c r="B10" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>137093771</v>
       </c>
       <c r="B11" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>137123335</v>
       </c>
       <c r="B12" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 34604-2026 artfynd.xlsx
+++ b/artfynd/A 34604-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093774</v>
       </c>
       <c r="B2" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137093765</v>
       </c>
       <c r="B3" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137093773</v>
       </c>
       <c r="B4" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>137093772</v>
       </c>
       <c r="B9" t="n">
-        <v>98224</v>
+        <v>98228</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>137093767</v>
       </c>
       <c r="B10" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>137093771</v>
       </c>
       <c r="B11" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>137123335</v>
       </c>
       <c r="B12" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 34604-2026 artfynd.xlsx
+++ b/artfynd/A 34604-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093774</v>
       </c>
       <c r="B2" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>137093772</v>
       </c>
       <c r="B9" t="n">
-        <v>98228</v>
+        <v>98230</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>137093767</v>
       </c>
       <c r="B10" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>137093771</v>
       </c>
       <c r="B11" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>137123335</v>
       </c>
       <c r="B12" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 34604-2026 artfynd.xlsx
+++ b/artfynd/A 34604-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093774</v>
       </c>
       <c r="B2" t="n">
-        <v>96586</v>
+        <v>96588</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137093765</v>
       </c>
       <c r="B3" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137093773</v>
       </c>
       <c r="B4" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>137093772</v>
       </c>
       <c r="B9" t="n">
-        <v>98230</v>
+        <v>98232</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>137093767</v>
       </c>
       <c r="B10" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>137093771</v>
       </c>
       <c r="B11" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>137123335</v>
       </c>
       <c r="B12" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 34604-2026 artfynd.xlsx
+++ b/artfynd/A 34604-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093774</v>
       </c>
       <c r="B2" t="n">
-        <v>96588</v>
+        <v>96601</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137093765</v>
       </c>
       <c r="B3" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137093773</v>
       </c>
       <c r="B4" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137093763</v>
       </c>
       <c r="B5" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>137093764</v>
       </c>
       <c r="B6" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>137093766</v>
       </c>
       <c r="B7" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>137093768</v>
       </c>
       <c r="B8" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>137093772</v>
       </c>
       <c r="B9" t="n">
-        <v>98232</v>
+        <v>98245</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>137093767</v>
       </c>
       <c r="B10" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>137093771</v>
       </c>
       <c r="B11" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>137123335</v>
       </c>
       <c r="B12" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 34604-2026 artfynd.xlsx
+++ b/artfynd/A 34604-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093774</v>
       </c>
       <c r="B2" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137093765</v>
       </c>
       <c r="B3" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137093773</v>
       </c>
       <c r="B4" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137093763</v>
       </c>
       <c r="B5" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>137093764</v>
       </c>
       <c r="B6" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>137093766</v>
       </c>
       <c r="B7" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>137093768</v>
       </c>
       <c r="B8" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>137093772</v>
       </c>
       <c r="B9" t="n">
-        <v>98245</v>
+        <v>98247</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>137093767</v>
       </c>
       <c r="B10" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>137093771</v>
       </c>
       <c r="B11" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>137123335</v>
       </c>
       <c r="B12" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 34604-2026 artfynd.xlsx
+++ b/artfynd/A 34604-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093774</v>
       </c>
       <c r="B2" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137093765</v>
       </c>
       <c r="B3" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137093773</v>
       </c>
       <c r="B4" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>137093772</v>
       </c>
       <c r="B9" t="n">
-        <v>98247</v>
+        <v>98250</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>137093767</v>
       </c>
       <c r="B10" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>137093771</v>
       </c>
       <c r="B11" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>137123335</v>
       </c>
       <c r="B12" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 34604-2026 artfynd.xlsx
+++ b/artfynd/A 34604-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093774</v>
       </c>
       <c r="B2" t="n">
-        <v>96606</v>
+        <v>96616</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137093765</v>
       </c>
       <c r="B3" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137093773</v>
       </c>
       <c r="B4" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137093763</v>
       </c>
       <c r="B5" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>137093764</v>
       </c>
       <c r="B6" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>137093766</v>
       </c>
       <c r="B7" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>137093768</v>
       </c>
       <c r="B8" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>137093772</v>
       </c>
       <c r="B9" t="n">
-        <v>98250</v>
+        <v>98260</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>137093767</v>
       </c>
       <c r="B10" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>137093771</v>
       </c>
       <c r="B11" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>137123335</v>
       </c>
       <c r="B12" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 34604-2026 artfynd.xlsx
+++ b/artfynd/A 34604-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093774</v>
       </c>
       <c r="B2" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137093765</v>
       </c>
       <c r="B3" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137093773</v>
       </c>
       <c r="B4" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>137093772</v>
       </c>
       <c r="B9" t="n">
-        <v>98260</v>
+        <v>98261</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>137093767</v>
       </c>
       <c r="B10" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>137093771</v>
       </c>
       <c r="B11" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>137123335</v>
       </c>
       <c r="B12" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 34604-2026 artfynd.xlsx
+++ b/artfynd/A 34604-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093774</v>
       </c>
       <c r="B2" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137093765</v>
       </c>
       <c r="B3" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137093773</v>
       </c>
       <c r="B4" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137093763</v>
       </c>
       <c r="B5" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>137093764</v>
       </c>
       <c r="B6" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>137093766</v>
       </c>
       <c r="B7" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>137093768</v>
       </c>
       <c r="B8" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>137093772</v>
       </c>
       <c r="B9" t="n">
-        <v>98261</v>
+        <v>98266</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>137093767</v>
       </c>
       <c r="B10" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>137093771</v>
       </c>
       <c r="B11" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>137123335</v>
       </c>
       <c r="B12" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 34604-2026 artfynd.xlsx
+++ b/artfynd/A 34604-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093774</v>
       </c>
       <c r="B2" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137093765</v>
       </c>
       <c r="B3" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137093773</v>
       </c>
       <c r="B4" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>137093772</v>
       </c>
       <c r="B9" t="n">
-        <v>98266</v>
+        <v>98268</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>137093767</v>
       </c>
       <c r="B10" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>137093771</v>
       </c>
       <c r="B11" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>137123335</v>
       </c>
       <c r="B12" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 34604-2026 artfynd.xlsx
+++ b/artfynd/A 34604-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093774</v>
       </c>
       <c r="B2" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137093765</v>
       </c>
       <c r="B3" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137093773</v>
       </c>
       <c r="B4" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>137093772</v>
       </c>
       <c r="B9" t="n">
-        <v>98268</v>
+        <v>98274</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>137093767</v>
       </c>
       <c r="B10" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>137093771</v>
       </c>
       <c r="B11" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>137123335</v>
       </c>
       <c r="B12" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 34604-2026 artfynd.xlsx
+++ b/artfynd/A 34604-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093774</v>
       </c>
       <c r="B2" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137093765</v>
       </c>
       <c r="B3" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137093773</v>
       </c>
       <c r="B4" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>137093772</v>
       </c>
       <c r="B9" t="n">
-        <v>98274</v>
+        <v>98286</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>137093767</v>
       </c>
       <c r="B10" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>137093771</v>
       </c>
       <c r="B11" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>137123335</v>
       </c>
       <c r="B12" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 34604-2026 artfynd.xlsx
+++ b/artfynd/A 34604-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093774</v>
       </c>
       <c r="B2" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137093765</v>
       </c>
       <c r="B3" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137093773</v>
       </c>
       <c r="B4" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>137093772</v>
       </c>
       <c r="B9" t="n">
-        <v>98286</v>
+        <v>98287</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>137093767</v>
       </c>
       <c r="B10" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>137093771</v>
       </c>
       <c r="B11" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>137123335</v>
       </c>
       <c r="B12" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 34604-2026 artfynd.xlsx
+++ b/artfynd/A 34604-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093774</v>
       </c>
       <c r="B2" t="n">
-        <v>96643</v>
+        <v>96646</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137093765</v>
       </c>
       <c r="B3" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137093773</v>
       </c>
       <c r="B4" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>137093772</v>
       </c>
       <c r="B9" t="n">
-        <v>98287</v>
+        <v>98290</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>137093767</v>
       </c>
       <c r="B10" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>137093771</v>
       </c>
       <c r="B11" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>137123335</v>
       </c>
       <c r="B12" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 34604-2026 artfynd.xlsx
+++ b/artfynd/A 34604-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ12"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -792,48 +792,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>137093765</v>
+        <v>137484373</v>
       </c>
       <c r="B3" t="n">
-        <v>93523</v>
+        <v>96646</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>2812</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Örsjön Knivsta kn, Upl</t>
+          <t>Örsjön, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>674762</v>
+        <v>674766</v>
       </c>
       <c r="R3" t="n">
-        <v>6634094</v>
+        <v>6633959</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,24 +887,24 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ylva Petersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ylva Petersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137093765</t>
+          <t>https://artportalen.se/Sighting/137484373</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>137093773</v>
+        <v>137093765</v>
       </c>
       <c r="B4" t="n">
         <v>93523</v>
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>674717</v>
+        <v>674762</v>
       </c>
       <c r="R4" t="n">
-        <v>6634112</v>
+        <v>6634094</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,38 +1010,38 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137093773</t>
+          <t>https://artportalen.se/Sighting/137093765</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>137093763</v>
+        <v>137093773</v>
       </c>
       <c r="B5" t="n">
-        <v>57221</v>
+        <v>93523</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,13 +1051,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>674499</v>
+        <v>674717</v>
       </c>
       <c r="R5" t="n">
-        <v>6633962</v>
+        <v>6634112</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,12 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:52</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Uppflog</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,51 +1122,51 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137093763</t>
+          <t>https://artportalen.se/Sighting/137093773</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137093764</v>
+        <v>137484374</v>
       </c>
       <c r="B6" t="n">
-        <v>57221</v>
+        <v>93523</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Örsjön Knivsta kn, Upl</t>
+          <t>Örsjön, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>674571</v>
+        <v>674770</v>
       </c>
       <c r="R6" t="n">
-        <v>6633993</v>
+        <v>6634026</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1198,27 +1193,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:52</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Uppflog</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,62 +1223,62 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ylva Petersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ylva Petersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137093764</t>
+          <t>https://artportalen.se/Sighting/137484374</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137093766</v>
+        <v>137484375</v>
       </c>
       <c r="B7" t="n">
-        <v>57221</v>
+        <v>93523</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Örsjön Knivsta kn, Upl</t>
+          <t>Örsjön, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>674739</v>
+        <v>674763</v>
       </c>
       <c r="R7" t="n">
-        <v>6634048</v>
+        <v>6634096</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1315,27 +1305,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:44</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Fjäder</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,24 +1335,24 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ylva Petersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ylva Petersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137093766</t>
+          <t>https://artportalen.se/Sighting/137484375</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>137093768</v>
+        <v>137093763</v>
       </c>
       <c r="B8" t="n">
         <v>57221</v>
@@ -1402,13 +1387,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>674721</v>
+        <v>674499</v>
       </c>
       <c r="R8" t="n">
-        <v>6633926</v>
+        <v>6633962</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1437,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,12 +1432,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Stjärtfjädrar</t>
+          <t>Uppflog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1478,16 +1463,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137093768</t>
+          <t>https://artportalen.se/Sighting/137093763</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>137093772</v>
+        <v>137093764</v>
       </c>
       <c r="B9" t="n">
-        <v>98290</v>
+        <v>57221</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1495,19 +1480,23 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221944</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1515,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>674777</v>
+        <v>674571</v>
       </c>
       <c r="R9" t="n">
-        <v>6634007</v>
+        <v>6633993</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1550,7 +1539,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1560,7 +1549,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Uppflog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1569,7 +1563,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1587,16 +1580,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137093772</t>
+          <t>https://artportalen.se/Sighting/137093764</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>137093767</v>
+        <v>137093766</v>
       </c>
       <c r="B10" t="n">
-        <v>101650</v>
+        <v>57221</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1604,21 +1597,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1628,10 +1621,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>674721</v>
+        <v>674739</v>
       </c>
       <c r="R10" t="n">
-        <v>6633952</v>
+        <v>6634048</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1663,7 +1656,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1673,7 +1666,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1699,16 +1697,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137093767</t>
+          <t>https://artportalen.se/Sighting/137093766</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>137093771</v>
+        <v>137093768</v>
       </c>
       <c r="B11" t="n">
-        <v>101650</v>
+        <v>57221</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1716,21 +1714,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1740,10 +1738,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>674761</v>
+        <v>674721</v>
       </c>
       <c r="R11" t="n">
-        <v>6633959</v>
+        <v>6633926</v>
       </c>
       <c r="S11" t="n">
         <v>7</v>
@@ -1775,7 +1773,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1785,7 +1783,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Stjärtfjädrar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1811,16 +1814,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137093771</t>
+          <t>https://artportalen.se/Sighting/137093768</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>137123335</v>
+        <v>137093772</v>
       </c>
       <c r="B12" t="n">
-        <v>101650</v>
+        <v>98290</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1828,37 +1831,33 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>221944</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Örsjön, Upl</t>
+          <t>Örsjön Knivsta kn, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>674763</v>
+        <v>674777</v>
       </c>
       <c r="R12" t="n">
-        <v>6634096</v>
+        <v>6634007</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1887,7 +1886,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1897,7 +1896,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1906,24 +1905,473 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ylva Petersson</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ylva Petersson</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137093772</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137093767</v>
+      </c>
+      <c r="B13" t="n">
+        <v>101650</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Örsjön Knivsta kn, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>674721</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6633952</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Husby-Långhundra</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137093767</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137093771</v>
+      </c>
+      <c r="B14" t="n">
+        <v>101650</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Örsjön Knivsta kn, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>674761</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6633959</v>
+      </c>
+      <c r="S14" t="n">
+        <v>7</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Husby-Långhundra</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137093771</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137123335</v>
+      </c>
+      <c r="B15" t="n">
+        <v>101650</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Örsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>674763</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6634096</v>
+      </c>
+      <c r="S15" t="n">
+        <v>8</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Husby-Långhundra</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Ylva Petersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Ylva Petersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/137123335</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>137484372</v>
+      </c>
+      <c r="B16" t="n">
+        <v>101650</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Örsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>674762</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6633961</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Husby-Långhundra</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Ylva Petersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Ylva Petersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137484372</t>
         </is>
       </c>
     </row>
@@ -1940,6 +2388,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34604-2026 artfynd.xlsx
+++ b/artfynd/A 34604-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093774</v>
       </c>
       <c r="B2" t="n">
-        <v>96646</v>
+        <v>96650</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137484373</v>
       </c>
       <c r="B3" t="n">
-        <v>96646</v>
+        <v>96650</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137093765</v>
       </c>
       <c r="B4" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137093773</v>
       </c>
       <c r="B5" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137484374</v>
       </c>
       <c r="B6" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137484375</v>
       </c>
       <c r="B7" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137093763</v>
       </c>
       <c r="B8" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>137093764</v>
       </c>
       <c r="B9" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>137093766</v>
       </c>
       <c r="B10" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>137093768</v>
       </c>
       <c r="B11" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>137093772</v>
       </c>
       <c r="B12" t="n">
-        <v>98290</v>
+        <v>98294</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>137093767</v>
       </c>
       <c r="B13" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>137093771</v>
       </c>
       <c r="B14" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>137123335</v>
       </c>
       <c r="B15" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>137484372</v>
       </c>
       <c r="B16" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
